--- a/backend/media/cmdbExcelTemplate/ImportNetworkTemplate.xlsx
+++ b/backend/media/cmdbExcelTemplate/ImportNetworkTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17940"/>
+    <workbookView windowHeight="7740"/>
   </bookViews>
   <sheets>
     <sheet name="cmdblist" sheetId="1" r:id="rId1"/>
@@ -15,9 +15,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="208">
-  <si>
-    <t>SN编码</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="93">
+  <si>
+    <t>SN号</t>
   </si>
   <si>
     <t>管理IP</t>
@@ -26,7 +26,7 @@
     <t>厂商</t>
   </si>
   <si>
-    <t>角色</t>
+    <t>设备角色</t>
   </si>
   <si>
     <t>网络区域</t>
@@ -47,13 +47,13 @@
     <t>机柜</t>
   </si>
   <si>
-    <t>U位</t>
-  </si>
-  <si>
-    <t>上线日期</t>
-  </si>
-  <si>
-    <t>使用状态</t>
+    <t>起始U位</t>
+  </si>
+  <si>
+    <t>结束U位</t>
+  </si>
+  <si>
+    <t>设备状态</t>
   </si>
   <si>
     <t>类型</t>
@@ -93,9 +93,6 @@
   </si>
   <si>
     <t>J05</t>
-  </si>
-  <si>
-    <t>11-11</t>
   </si>
   <si>
     <t>在线</t>
@@ -124,535 +121,193 @@
 备注：无要求</t>
   </si>
   <si>
+    <t>角色</t>
+  </si>
+  <si>
+    <t>使用状态</t>
+  </si>
+  <si>
     <t>华三</t>
   </si>
   <si>
     <t>Border</t>
   </si>
   <si>
+    <t>SSLVPN</t>
+  </si>
+  <si>
+    <t>华为</t>
+  </si>
+  <si>
+    <t>FW</t>
+  </si>
+  <si>
+    <t>二层</t>
+  </si>
+  <si>
+    <t>下线</t>
+  </si>
+  <si>
+    <t>TAP交换机</t>
+  </si>
+  <si>
+    <t>锐捷</t>
+  </si>
+  <si>
+    <t>IPMI</t>
+  </si>
+  <si>
+    <t>大二层</t>
+  </si>
+  <si>
+    <t>挂牌</t>
+  </si>
+  <si>
+    <t>交换机</t>
+  </si>
+  <si>
+    <t>山石网科</t>
+  </si>
+  <si>
+    <t>IPMI接入</t>
+  </si>
+  <si>
+    <t>备用</t>
+  </si>
+  <si>
+    <t>服务器</t>
+  </si>
+  <si>
+    <t>思科</t>
+  </si>
+  <si>
+    <t>LB</t>
+  </si>
+  <si>
+    <t>负载均衡</t>
+  </si>
+  <si>
+    <t>中兴</t>
+  </si>
+  <si>
+    <t>leaf</t>
+  </si>
+  <si>
+    <t>盛科</t>
+  </si>
+  <si>
+    <t>NetDevOps服务器</t>
+  </si>
+  <si>
+    <t>防火墙</t>
+  </si>
+  <si>
+    <t>科来</t>
+  </si>
+  <si>
+    <t>POP点</t>
+  </si>
+  <si>
+    <t>Mellanox</t>
+  </si>
+  <si>
+    <t>spine</t>
+  </si>
+  <si>
+    <t>戴尔</t>
+  </si>
+  <si>
+    <t>Super-Spine</t>
+  </si>
+  <si>
+    <t>F5</t>
+  </si>
+  <si>
+    <t>TAP万兆接入</t>
+  </si>
+  <si>
+    <t>迈普</t>
+  </si>
+  <si>
+    <t>TAP接入</t>
+  </si>
+  <si>
+    <t>Citrix</t>
+  </si>
+  <si>
+    <t>VTEP</t>
+  </si>
+  <si>
+    <t>万兆光口接入</t>
+  </si>
+  <si>
+    <t>浪潮思科</t>
+  </si>
+  <si>
+    <t>绿盟</t>
+  </si>
+  <si>
+    <t>万兆电口接入</t>
+  </si>
+  <si>
+    <t>成都数维</t>
+  </si>
+  <si>
+    <t>业务互联</t>
+  </si>
+  <si>
+    <t>业务互联区域</t>
+  </si>
+  <si>
+    <t>二层汇聚</t>
+  </si>
+  <si>
+    <t>互联边界</t>
+  </si>
+  <si>
     <t>公共运维区域</t>
   </si>
   <si>
-    <t>公网网络</t>
-  </si>
-  <si>
-    <t>SSLVPN</t>
-  </si>
-  <si>
-    <t>华为</t>
-  </si>
-  <si>
-    <t>FW</t>
-  </si>
-  <si>
-    <t>公共集群</t>
-  </si>
-  <si>
-    <t>测试网络</t>
-  </si>
-  <si>
-    <t>二层</t>
-  </si>
-  <si>
-    <t>北京鲁谷</t>
-  </si>
-  <si>
-    <t>8栋4层A区</t>
-  </si>
-  <si>
-    <t>下线</t>
-  </si>
-  <si>
-    <t>TAP交换机</t>
-  </si>
-  <si>
-    <t>锐捷</t>
-  </si>
-  <si>
-    <t>IPMI</t>
-  </si>
-  <si>
-    <t>公共集群区域</t>
-  </si>
-  <si>
-    <t>大二层</t>
-  </si>
-  <si>
-    <t>广州华新园</t>
-  </si>
-  <si>
-    <t>5号</t>
-  </si>
-  <si>
-    <t>挂牌</t>
-  </si>
-  <si>
-    <t>交换机</t>
-  </si>
-  <si>
-    <t>山石网科</t>
-  </si>
-  <si>
-    <t>IPMI接入</t>
-  </si>
-  <si>
-    <t>研发网络</t>
-  </si>
-  <si>
-    <t>上海嘉定</t>
-  </si>
-  <si>
-    <t>备用</t>
-  </si>
-  <si>
-    <t>服务器</t>
-  </si>
-  <si>
-    <t>思科</t>
-  </si>
-  <si>
-    <t>LB</t>
+    <t>公网网关</t>
+  </si>
+  <si>
+    <t>冷备</t>
+  </si>
+  <si>
+    <t>出口防火墙</t>
   </si>
   <si>
     <t>千兆电口接入</t>
   </si>
   <si>
-    <t>研测网络</t>
-  </si>
-  <si>
-    <t>合肥南岗</t>
-  </si>
-  <si>
-    <t>负载均衡</t>
-  </si>
-  <si>
-    <t>中兴</t>
-  </si>
-  <si>
-    <t>leaf</t>
-  </si>
-  <si>
-    <t>千兆研测区域</t>
-  </si>
-  <si>
-    <t>骨干网络</t>
-  </si>
-  <si>
-    <t>北京大族</t>
-  </si>
-  <si>
-    <t>2-核心网络机房</t>
-  </si>
-  <si>
-    <t>盛科</t>
-  </si>
-  <si>
-    <t>NetDevOps服务器</t>
-  </si>
-  <si>
-    <t>原语音云区域</t>
-  </si>
-  <si>
-    <t>合肥A2</t>
-  </si>
-  <si>
-    <t>A2栋3-4号</t>
-  </si>
-  <si>
-    <t>防火墙</t>
-  </si>
-  <si>
-    <t>科来</t>
-  </si>
-  <si>
-    <t>POP点</t>
-  </si>
-  <si>
-    <t>合肥教育云</t>
-  </si>
-  <si>
-    <t>天都路电信机房</t>
-  </si>
-  <si>
-    <t>A2栋3-3号</t>
-  </si>
-  <si>
-    <t>Mellanox</t>
-  </si>
-  <si>
-    <t>spine</t>
-  </si>
-  <si>
-    <t>听见网络区域</t>
-  </si>
-  <si>
-    <t>北京日上</t>
-  </si>
-  <si>
-    <t>A2栋3-2号</t>
-  </si>
-  <si>
-    <t>戴尔</t>
-  </si>
-  <si>
-    <t>Super-Spine</t>
-  </si>
-  <si>
-    <t>品高虚拟化</t>
-  </si>
-  <si>
-    <t>北京酒仙桥</t>
-  </si>
-  <si>
-    <t>A2栋2-4号</t>
-  </si>
-  <si>
-    <t>F5</t>
-  </si>
-  <si>
-    <t>TAP万兆接入</t>
-  </si>
-  <si>
-    <t>外研讯飞网络区域</t>
-  </si>
-  <si>
-    <t>北京中信</t>
-  </si>
-  <si>
-    <t>A2栋2-3号</t>
-  </si>
-  <si>
-    <t>迈普</t>
-  </si>
-  <si>
-    <t>TAP接入</t>
-  </si>
-  <si>
-    <t>外联区</t>
-  </si>
-  <si>
-    <t>上海临港</t>
-  </si>
-  <si>
-    <t>A2栋2-2号</t>
-  </si>
-  <si>
-    <t>Citrix</t>
-  </si>
-  <si>
-    <t>VTEP</t>
-  </si>
-  <si>
-    <t>外部互联区域</t>
-  </si>
-  <si>
-    <t>香港将军澳</t>
-  </si>
-  <si>
-    <t>12栋5层B区</t>
-  </si>
-  <si>
-    <t>万兆光口接入</t>
-  </si>
-  <si>
-    <t>大模型业务面</t>
-  </si>
-  <si>
-    <t>合肥城市云</t>
-  </si>
-  <si>
-    <t>12栋4层A区</t>
-  </si>
-  <si>
-    <t>浪潮思科</t>
-  </si>
-  <si>
-    <t>大模型参数面</t>
-  </si>
-  <si>
-    <t>苏州超算</t>
-  </si>
-  <si>
-    <t>2号</t>
-  </si>
-  <si>
-    <t>绿盟</t>
-  </si>
-  <si>
-    <t>万兆电口接入</t>
-  </si>
-  <si>
-    <t>大模型数据面</t>
-  </si>
-  <si>
-    <t>4-1号</t>
-  </si>
-  <si>
-    <t>成都数维</t>
-  </si>
-  <si>
-    <t>业务互联</t>
-  </si>
-  <si>
-    <t>安徽教育云</t>
-  </si>
-  <si>
-    <t>业务互联区域</t>
-  </si>
-  <si>
-    <t>客服信息化</t>
-  </si>
-  <si>
-    <t>运营商机房2</t>
-  </si>
-  <si>
-    <t>二层汇聚</t>
-  </si>
-  <si>
-    <t>寰宇研发网</t>
-  </si>
-  <si>
-    <t>运营商机房1</t>
-  </si>
-  <si>
-    <t>互联边界</t>
-  </si>
-  <si>
-    <t>广告网络区域</t>
-  </si>
-  <si>
-    <t>4F</t>
-  </si>
-  <si>
-    <t>政法IAAS区域</t>
-  </si>
-  <si>
-    <t>114号</t>
-  </si>
-  <si>
-    <t>公网网关</t>
-  </si>
-  <si>
-    <t>教育BG外地交付项目</t>
-  </si>
-  <si>
-    <t>4-4号</t>
-  </si>
-  <si>
-    <t>冷备</t>
-  </si>
-  <si>
-    <t>教育BG酒仙桥双中心</t>
-  </si>
-  <si>
-    <t>4-2号</t>
-  </si>
-  <si>
-    <t>出口防火墙</t>
-  </si>
-  <si>
-    <t>教育PaaS应用托管平台</t>
-  </si>
-  <si>
-    <t>核心网络机房</t>
-  </si>
-  <si>
-    <t>教育中台区域</t>
-  </si>
-  <si>
-    <t>1号</t>
-  </si>
-  <si>
     <t>接入</t>
   </si>
   <si>
-    <t>教育私有云</t>
-  </si>
-  <si>
-    <t>12栋4层B区</t>
-  </si>
-  <si>
     <t>接入交换机</t>
   </si>
   <si>
-    <t>日上1</t>
-  </si>
-  <si>
-    <t>星河智联</t>
-  </si>
-  <si>
     <t>核心交换机</t>
   </si>
   <si>
-    <t>智学网络区域</t>
-  </si>
-  <si>
-    <t>4-5号</t>
-  </si>
-  <si>
     <t>核心网络</t>
   </si>
   <si>
-    <t>智慧医疗网络区域</t>
-  </si>
-  <si>
     <t>汇聚</t>
   </si>
   <si>
-    <t>服务器带外管理</t>
-  </si>
-  <si>
     <t>网关汇聚</t>
   </si>
   <si>
-    <t>服务器管理区域</t>
-  </si>
-  <si>
-    <t>4-核心网络机房</t>
-  </si>
-  <si>
-    <t>核心区域</t>
-  </si>
-  <si>
     <t>边界互联</t>
   </si>
   <si>
-    <t>核心区域1</t>
-  </si>
-  <si>
     <t>隔离防火墙</t>
   </si>
   <si>
-    <t>核心区域2</t>
-  </si>
-  <si>
     <t>骨干POP</t>
   </si>
   <si>
-    <t>测试环境</t>
-  </si>
-  <si>
     <t>骨干接入</t>
-  </si>
-  <si>
-    <t>测试网络区域</t>
-  </si>
-  <si>
-    <t>2-2号</t>
-  </si>
-  <si>
-    <t>消费者BG区域</t>
-  </si>
-  <si>
-    <t>生产IAAS管理区域</t>
-  </si>
-  <si>
-    <t>生产公共区域</t>
-  </si>
-  <si>
-    <t>生产网IAAS</t>
-  </si>
-  <si>
-    <t>3号</t>
-  </si>
-  <si>
-    <t>电口接入区域</t>
-  </si>
-  <si>
-    <t>测试机房</t>
-  </si>
-  <si>
-    <t>研发网IAAS</t>
-  </si>
-  <si>
-    <t>3-核心网络机房</t>
-  </si>
-  <si>
-    <t>研发网络区域</t>
-  </si>
-  <si>
-    <t>研测IAAS管理区域</t>
-  </si>
-  <si>
-    <t>研测网IAAS</t>
-  </si>
-  <si>
-    <t>研测网络区域</t>
-  </si>
-  <si>
-    <t>7号</t>
-  </si>
-  <si>
-    <t>研测虚拟化</t>
-  </si>
-  <si>
-    <t>C4栋1-1号</t>
-  </si>
-  <si>
-    <t>科讯嘉联区域</t>
-  </si>
-  <si>
-    <t>12栋3层B区</t>
-  </si>
-  <si>
-    <t>移动互联区域</t>
-  </si>
-  <si>
-    <t>C4栋3-1号</t>
-  </si>
-  <si>
-    <t>C4栋2-1号</t>
-  </si>
-  <si>
-    <t>网域隔离区</t>
-  </si>
-  <si>
-    <t>C4栋4-1号</t>
-  </si>
-  <si>
-    <t>网络TAP区域</t>
-  </si>
-  <si>
-    <t>1-运营商机房1</t>
-  </si>
-  <si>
-    <t>网络带外管理</t>
-  </si>
-  <si>
-    <t>1-运营商机房2</t>
-  </si>
-  <si>
-    <t>网络管理区</t>
-  </si>
-  <si>
-    <t>2-4号</t>
-  </si>
-  <si>
-    <t>网络管理区域</t>
-  </si>
-  <si>
-    <t>3-2号</t>
-  </si>
-  <si>
-    <t>集群边界</t>
-  </si>
-  <si>
-    <t>3-5号</t>
-  </si>
-  <si>
-    <t>3-4号</t>
-  </si>
-  <si>
-    <t>骨干网络区域</t>
-  </si>
-  <si>
-    <t>2-3号</t>
-  </si>
-  <si>
-    <t>3-3号</t>
-  </si>
-  <si>
-    <t>3-1号</t>
   </si>
 </sst>
 </file>
@@ -664,7 +319,7 @@
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -1287,17 +942,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
@@ -1634,11 +1289,11 @@
     <col min="5" max="6" width="9.55833333333333" customWidth="1"/>
     <col min="7" max="7" width="10.5583333333333" customWidth="1"/>
     <col min="8" max="8" width="7.55833333333333" customWidth="1"/>
-    <col min="9" max="9" width="13.8833333333333" customWidth="1"/>
+    <col min="9" max="9" width="10.625" customWidth="1"/>
     <col min="10" max="10" width="6.55833333333333" customWidth="1"/>
-    <col min="11" max="11" width="9.375" style="3" customWidth="1"/>
-    <col min="12" max="12" width="11.375" customWidth="1"/>
-    <col min="13" max="14" width="10.4416666666667" customWidth="1"/>
+    <col min="11" max="12" width="7.875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="8.875" customWidth="1"/>
+    <col min="14" max="14" width="10.4416666666667" customWidth="1"/>
     <col min="15" max="15" width="24.8833333333333" customWidth="1"/>
     <col min="16" max="16" width="29.1083333333333" customWidth="1"/>
   </cols>
@@ -1674,7 +1329,7 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="L1" t="s">
@@ -1689,7 +1344,7 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1724,53 +1379,41 @@
       <c r="J2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="7">
+        <v>11</v>
+      </c>
+      <c r="L2" s="7">
+        <v>11</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="7">
-        <v>45740</v>
-      </c>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>30</v>
-      </c>
     </row>
   </sheetData>
-  <dataValidations count="9">
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
+      <formula1>下拉列表!$E$2:$E$4</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576">
       <formula1>下拉列表!$A$2:$A$19</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576">
-      <formula1>下拉列表!$C$2:$C$60</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576">
-      <formula1>下拉列表!$G$2:$G$62</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576">
-      <formula1>下拉列表!$F$2:$F$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
-      <formula1>下拉列表!$E$2:$E$4</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576">
+      <formula1>下拉列表!$J$2:$J$8</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M1048576">
       <formula1>下拉列表!$I$2:$I$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
       <formula1>下拉列表!$B$2:$B$38</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576">
-      <formula1>下拉列表!$D$2:$D$7</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576">
-      <formula1>下拉列表!$J$2:$J$8</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1782,7 +1425,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1790,7 +1433,7 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s">
         <v>4</v>
@@ -1811,7 +1454,7 @@
         <v>9</v>
       </c>
       <c r="I1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="J1" t="s">
         <v>13</v>
@@ -1819,755 +1462,307 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" t="s">
         <v>33</v>
-      </c>
-      <c r="D2" t="s">
-        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>22</v>
       </c>
-      <c r="F2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
-      </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
         <v>36</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
         <v>37</v>
       </c>
-      <c r="C3" t="s">
+      <c r="I3" t="s">
         <v>38</v>
       </c>
-      <c r="D3" t="s">
+      <c r="J3" t="s">
         <v>39</v>
-      </c>
-      <c r="E3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I4" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="J4" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G5">
-        <v>501</v>
+        <v>46</v>
       </c>
       <c r="I5" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="J5" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" t="s">
-        <v>62</v>
-      </c>
-      <c r="F6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G6">
-        <v>201</v>
+        <v>50</v>
       </c>
       <c r="J6" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" t="s">
-        <v>68</v>
-      </c>
-      <c r="F7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G7" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="J7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G8" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="J8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" t="s">
-        <v>79</v>
-      </c>
-      <c r="F9" t="s">
-        <v>80</v>
-      </c>
-      <c r="G9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" t="s">
-        <v>84</v>
-      </c>
-      <c r="F10" t="s">
-        <v>85</v>
-      </c>
-      <c r="G10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C11" t="s">
-        <v>89</v>
-      </c>
-      <c r="F11" t="s">
-        <v>90</v>
-      </c>
-      <c r="G11" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" t="s">
-        <v>94</v>
-      </c>
-      <c r="F12" t="s">
-        <v>95</v>
-      </c>
-      <c r="G12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C13" t="s">
-        <v>99</v>
-      </c>
-      <c r="F13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" t="s">
-        <v>104</v>
-      </c>
-      <c r="F14" t="s">
-        <v>105</v>
-      </c>
-      <c r="G14" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C15" t="s">
-        <v>108</v>
-      </c>
-      <c r="F15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G15" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="B16" t="s">
         <v>19</v>
       </c>
-      <c r="C16" t="s">
-        <v>112</v>
-      </c>
-      <c r="F16" t="s">
-        <v>113</v>
-      </c>
-      <c r="G16" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="B17" t="s">
-        <v>116</v>
-      </c>
-      <c r="C17" t="s">
-        <v>117</v>
-      </c>
-      <c r="G17" t="s">
-        <v>118</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="B18" t="s">
-        <v>120</v>
-      </c>
-      <c r="C18" t="s">
-        <v>121</v>
-      </c>
-      <c r="G18" s="1">
-        <v>45689</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>74</v>
+      </c>
+      <c r="G18" s="1"/>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>122</v>
-      </c>
-      <c r="C19" t="s">
-        <v>123</v>
-      </c>
-      <c r="G19" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>125</v>
-      </c>
-      <c r="C20" t="s">
-        <v>126</v>
-      </c>
-      <c r="G20" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
       <c r="B21" t="s">
-        <v>128</v>
-      </c>
-      <c r="C21" t="s">
-        <v>129</v>
-      </c>
-      <c r="G21" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" t="s">
-        <v>131</v>
-      </c>
-      <c r="G22" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>133</v>
-      </c>
-      <c r="C23" t="s">
-        <v>134</v>
-      </c>
-      <c r="G23" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
       <c r="B24" t="s">
-        <v>136</v>
-      </c>
-      <c r="C24" t="s">
-        <v>137</v>
-      </c>
-      <c r="G24" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>139</v>
-      </c>
-      <c r="C25" t="s">
-        <v>140</v>
-      </c>
-      <c r="G25" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
       <c r="B26" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" t="s">
-        <v>142</v>
-      </c>
-      <c r="G26" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>144</v>
-      </c>
-      <c r="C27" t="s">
-        <v>145</v>
-      </c>
-      <c r="G27" t="s">
-        <v>146</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="2:7">
       <c r="B28" t="s">
-        <v>147</v>
-      </c>
-      <c r="C28" t="s">
-        <v>148</v>
-      </c>
-      <c r="G28" s="1">
-        <v>45692</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="G28" s="1"/>
     </row>
     <row r="29" spans="2:7">
       <c r="B29" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" t="s">
-        <v>149</v>
-      </c>
-      <c r="G29" s="1">
-        <v>45717</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7">
+        <v>48</v>
+      </c>
+      <c r="G29" s="1"/>
+    </row>
+    <row r="30" spans="2:2">
       <c r="B30" t="s">
-        <v>150</v>
-      </c>
-      <c r="C30" t="s">
-        <v>151</v>
-      </c>
-      <c r="G30" t="s">
-        <v>152</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="2:7">
       <c r="B31" t="s">
-        <v>153</v>
-      </c>
-      <c r="C31" t="s">
-        <v>154</v>
-      </c>
-      <c r="G31" s="1">
-        <v>45690</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="G31" s="1"/>
     </row>
     <row r="32" spans="2:7">
       <c r="B32" t="s">
-        <v>155</v>
-      </c>
-      <c r="C32" t="s">
-        <v>156</v>
-      </c>
-      <c r="G32" s="1">
-        <v>45658</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7">
+        <v>87</v>
+      </c>
+      <c r="G32" s="1"/>
+    </row>
+    <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>157</v>
-      </c>
-      <c r="C33" t="s">
-        <v>158</v>
-      </c>
-      <c r="G33" t="s">
-        <v>159</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="2:7">
       <c r="B34" t="s">
-        <v>64</v>
-      </c>
-      <c r="C34" t="s">
-        <v>160</v>
-      </c>
-      <c r="G34" s="1">
-        <v>45719</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="G34" s="1"/>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" t="s">
-        <v>161</v>
-      </c>
-      <c r="C35" t="s">
-        <v>162</v>
-      </c>
-      <c r="G35" s="1">
-        <v>45719</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="G35" s="1"/>
     </row>
     <row r="36" spans="2:7">
       <c r="B36" t="s">
-        <v>163</v>
-      </c>
-      <c r="C36" t="s">
-        <v>164</v>
-      </c>
-      <c r="G36" s="1">
-        <v>45691</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7">
+        <v>90</v>
+      </c>
+      <c r="G36" s="1"/>
+    </row>
+    <row r="37" spans="2:2">
       <c r="B37" t="s">
-        <v>165</v>
-      </c>
-      <c r="C37" t="s">
-        <v>166</v>
-      </c>
-      <c r="G37">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
       <c r="B38" t="s">
-        <v>167</v>
-      </c>
-      <c r="C38" t="s">
-        <v>168</v>
-      </c>
-      <c r="G38" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="39" spans="3:7">
-      <c r="C39" t="s">
-        <v>170</v>
-      </c>
-      <c r="G39" s="1">
-        <v>45718</v>
-      </c>
-    </row>
-    <row r="40" spans="3:7">
-      <c r="C40" t="s">
-        <v>171</v>
-      </c>
-      <c r="G40" s="1">
-        <v>45721</v>
-      </c>
-    </row>
-    <row r="41" spans="3:7">
-      <c r="C41" t="s">
-        <v>172</v>
-      </c>
-      <c r="G41" s="1">
-        <v>45718</v>
-      </c>
-    </row>
-    <row r="42" spans="3:7">
-      <c r="C42" t="s">
-        <v>173</v>
-      </c>
-      <c r="G42" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="43" spans="3:7">
-      <c r="C43" t="s">
-        <v>175</v>
-      </c>
-      <c r="G43" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="44" spans="3:7">
-      <c r="C44" t="s">
-        <v>177</v>
-      </c>
-      <c r="G44" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="45" spans="3:7">
-      <c r="C45" t="s">
-        <v>179</v>
-      </c>
-      <c r="G45">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="46" spans="3:7">
-      <c r="C46" t="s">
-        <v>180</v>
-      </c>
-      <c r="G46" s="1">
-        <v>45720</v>
-      </c>
-    </row>
-    <row r="47" spans="3:7">
-      <c r="C47" t="s">
-        <v>181</v>
-      </c>
-      <c r="G47" s="1">
-        <v>45751</v>
-      </c>
-    </row>
-    <row r="48" spans="3:7">
-      <c r="C48" t="s">
-        <v>182</v>
-      </c>
-      <c r="G48" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="49" spans="3:7">
-      <c r="C49" t="s">
-        <v>184</v>
-      </c>
-      <c r="G49" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="50" spans="3:7">
-      <c r="C50" t="s">
-        <v>186</v>
-      </c>
-      <c r="G50" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="51" spans="3:7">
-      <c r="C51" t="s">
-        <v>188</v>
-      </c>
-      <c r="G51" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="52" spans="3:7">
-      <c r="C52" t="s">
-        <v>157</v>
-      </c>
-      <c r="G52" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="53" spans="3:7">
-      <c r="C53" t="s">
-        <v>191</v>
-      </c>
-      <c r="G53" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="54" spans="3:7">
-      <c r="C54" t="s">
-        <v>193</v>
-      </c>
-      <c r="G54" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="55" spans="3:7">
-      <c r="C55" t="s">
-        <v>195</v>
-      </c>
-      <c r="G55" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="56" spans="3:7">
-      <c r="C56" t="s">
-        <v>197</v>
-      </c>
-      <c r="G56" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="57" spans="3:7">
-      <c r="C57" t="s">
-        <v>199</v>
-      </c>
-      <c r="G57" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="58" spans="3:7">
-      <c r="C58" t="s">
-        <v>201</v>
-      </c>
-      <c r="G58" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="59" spans="3:7">
-      <c r="C59" t="s">
-        <v>167</v>
-      </c>
-      <c r="G59" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="60" spans="3:7">
-      <c r="C60" t="s">
-        <v>204</v>
-      </c>
-      <c r="G60" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="61" spans="7:7">
-      <c r="G61" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="62" spans="7:7">
-      <c r="G62" t="s">
-        <v>207</v>
-      </c>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="7:7">
+      <c r="G39" s="1"/>
+    </row>
+    <row r="40" spans="7:7">
+      <c r="G40" s="1"/>
+    </row>
+    <row r="41" spans="7:7">
+      <c r="G41" s="1"/>
+    </row>
+    <row r="46" spans="7:7">
+      <c r="G46" s="1"/>
+    </row>
+    <row r="47" spans="7:7">
+      <c r="G47" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/media/cmdbExcelTemplate/ImportNetworkTemplate.xlsx
+++ b/backend/media/cmdbExcelTemplate/ImportNetworkTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="7740"/>
+    <workbookView windowHeight="17940"/>
   </bookViews>
   <sheets>
     <sheet name="cmdblist" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="90">
   <si>
     <t>SN号</t>
   </si>
@@ -23,174 +23,151 @@
     <t>管理IP</t>
   </si>
   <si>
+    <t>网络架构</t>
+  </si>
+  <si>
     <t>厂商</t>
   </si>
   <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>机房</t>
+  </si>
+  <si>
+    <t>模块</t>
+  </si>
+  <si>
+    <t>机柜</t>
+  </si>
+  <si>
     <t>设备角色</t>
   </si>
   <si>
     <t>网络区域</t>
   </si>
   <si>
+    <t>起始U位</t>
+  </si>
+  <si>
+    <t>结束U位</t>
+  </si>
+  <si>
+    <t>设备状态</t>
+  </si>
+  <si>
     <t>网络属性</t>
   </si>
   <si>
-    <t>网络架构</t>
-  </si>
-  <si>
-    <t>机房</t>
-  </si>
-  <si>
-    <t>模块</t>
-  </si>
-  <si>
-    <t>机柜</t>
-  </si>
-  <si>
-    <t>起始U位</t>
-  </si>
-  <si>
-    <t>结束U位</t>
-  </si>
-  <si>
-    <t>设备状态</t>
-  </si>
-  <si>
-    <t>类型</t>
-  </si>
-  <si>
     <t>备注</t>
   </si>
   <si>
-    <t>填写说明</t>
-  </si>
-  <si>
     <t>SN1107500140038130</t>
   </si>
   <si>
     <t>172.16.75.253</t>
   </si>
   <si>
+    <t>三层</t>
+  </si>
+  <si>
     <t>深信服</t>
   </si>
   <si>
+    <t>交换机</t>
+  </si>
+  <si>
+    <t>合肥B3</t>
+  </si>
+  <si>
+    <t>4-3号</t>
+  </si>
+  <si>
+    <t>J05</t>
+  </si>
+  <si>
     <t>万兆接入</t>
   </si>
   <si>
     <t>公网区域</t>
   </si>
   <si>
+    <t>在线</t>
+  </si>
+  <si>
     <t>生产网络</t>
   </si>
   <si>
-    <t>三层</t>
-  </si>
-  <si>
-    <t>合肥B3</t>
-  </si>
-  <si>
-    <t>4-3号</t>
-  </si>
-  <si>
-    <t>J05</t>
-  </si>
-  <si>
-    <t>在线</t>
+    <t>教育公共综合业务防火墙</t>
+  </si>
+  <si>
+    <t>使用状态</t>
+  </si>
+  <si>
+    <t>华三</t>
+  </si>
+  <si>
+    <t>Border</t>
+  </si>
+  <si>
+    <t>SSLVPN</t>
+  </si>
+  <si>
+    <t>华为</t>
+  </si>
+  <si>
+    <t>FW</t>
+  </si>
+  <si>
+    <t>二层</t>
+  </si>
+  <si>
+    <t>下线</t>
+  </si>
+  <si>
+    <t>TAP交换机</t>
+  </si>
+  <si>
+    <t>锐捷</t>
+  </si>
+  <si>
+    <t>IPMI</t>
+  </si>
+  <si>
+    <t>大二层</t>
+  </si>
+  <si>
+    <t>挂牌</t>
+  </si>
+  <si>
+    <t>山石网科</t>
+  </si>
+  <si>
+    <t>IPMI接入</t>
+  </si>
+  <si>
+    <t>备用</t>
+  </si>
+  <si>
+    <t>服务器</t>
+  </si>
+  <si>
+    <t>思科</t>
+  </si>
+  <si>
+    <t>LB</t>
+  </si>
+  <si>
+    <t>负载均衡</t>
+  </si>
+  <si>
+    <t>中兴</t>
+  </si>
+  <si>
+    <t>leaf</t>
   </si>
   <si>
     <t>路由器</t>
-  </si>
-  <si>
-    <t>教育公共综合业务防火墙</t>
-  </si>
-  <si>
-    <t>填写时请将第二列示例删除。
-SN编码：必填，无要求
-管理IP：正确的IP格式
-厂商：下拉选择
-角色：确认CMDB已录入
-网络区域：确认CMDB已录入
-网络属性:下拉选择
-网络架构：下拉选择
-机房：下拉选择
-模块：确认CMDB已录入后填写
-机柜：确认CMDB已录入填写
-U位：确认CMDB已录入填写
-上线日期：可不填,默认为当前日期。格式2019/9/1
-使用状态：下拉选择
-备注：无要求</t>
-  </si>
-  <si>
-    <t>角色</t>
-  </si>
-  <si>
-    <t>使用状态</t>
-  </si>
-  <si>
-    <t>华三</t>
-  </si>
-  <si>
-    <t>Border</t>
-  </si>
-  <si>
-    <t>SSLVPN</t>
-  </si>
-  <si>
-    <t>华为</t>
-  </si>
-  <si>
-    <t>FW</t>
-  </si>
-  <si>
-    <t>二层</t>
-  </si>
-  <si>
-    <t>下线</t>
-  </si>
-  <si>
-    <t>TAP交换机</t>
-  </si>
-  <si>
-    <t>锐捷</t>
-  </si>
-  <si>
-    <t>IPMI</t>
-  </si>
-  <si>
-    <t>大二层</t>
-  </si>
-  <si>
-    <t>挂牌</t>
-  </si>
-  <si>
-    <t>交换机</t>
-  </si>
-  <si>
-    <t>山石网科</t>
-  </si>
-  <si>
-    <t>IPMI接入</t>
-  </si>
-  <si>
-    <t>备用</t>
-  </si>
-  <si>
-    <t>服务器</t>
-  </si>
-  <si>
-    <t>思科</t>
-  </si>
-  <si>
-    <t>LB</t>
-  </si>
-  <si>
-    <t>负载均衡</t>
-  </si>
-  <si>
-    <t>中兴</t>
-  </si>
-  <si>
-    <t>leaf</t>
   </si>
   <si>
     <t>盛科</t>
@@ -314,12 +291,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -932,33 +908,27 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1279,141 +1249,135 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="20.4416666666667" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="9.55833333333333" customWidth="1"/>
-    <col min="4" max="4" width="11.6666666666667" customWidth="1"/>
-    <col min="5" max="6" width="9.55833333333333" customWidth="1"/>
-    <col min="7" max="7" width="10.5583333333333" customWidth="1"/>
-    <col min="8" max="8" width="7.55833333333333" customWidth="1"/>
-    <col min="9" max="9" width="10.625" customWidth="1"/>
-    <col min="10" max="10" width="6.55833333333333" customWidth="1"/>
-    <col min="11" max="12" width="7.875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.75" customWidth="1"/>
+    <col min="3" max="3" width="11.125" customWidth="1"/>
+    <col min="4" max="4" width="9.55833333333333" customWidth="1"/>
+    <col min="5" max="5" width="10.4416666666667" customWidth="1"/>
+    <col min="6" max="6" width="8.5" customWidth="1"/>
+    <col min="7" max="7" width="7.875" customWidth="1"/>
+    <col min="8" max="8" width="6.55833333333333" customWidth="1"/>
+    <col min="9" max="9" width="11.125" customWidth="1"/>
+    <col min="10" max="10" width="9.55833333333333" customWidth="1"/>
+    <col min="11" max="12" width="7.875" style="2" customWidth="1"/>
     <col min="13" max="13" width="8.875" customWidth="1"/>
-    <col min="14" max="14" width="10.4416666666667" customWidth="1"/>
+    <col min="14" max="14" width="10.875" customWidth="1"/>
     <col min="15" max="15" width="24.8833333333333" customWidth="1"/>
-    <col min="16" max="16" width="29.1083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.4" customHeight="1" spans="1:16">
-      <c r="A1" t="s">
+    <row r="1" ht="14.4" customHeight="1" spans="1:15">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="6" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" ht="24" customHeight="1" spans="1:15">
+      <c r="A2" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" ht="24" customHeight="1" spans="1:16">
-      <c r="A2" s="4" t="s">
+      <c r="B2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="6">
+        <v>11</v>
+      </c>
+      <c r="L2" s="6">
+        <v>11</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="7">
-        <v>11</v>
-      </c>
-      <c r="L2" s="7">
-        <v>11</v>
-      </c>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
-      <formula1>下拉列表!$E$2:$E$4</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2 I3:I1048576">
+      <formula1>下拉列表!$B$2:$B$39</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2 E3:E1048576">
+      <formula1>下拉列表!$E$2:$E$8</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2 C3:C1048576">
+      <formula1>下拉列表!$C$2:$C$4</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2 D3:D1048576">
       <formula1>下拉列表!$A$2:$A$19</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576">
-      <formula1>下拉列表!$J$2:$J$8</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M1048576">
-      <formula1>下拉列表!$I$2:$I$5</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
-      <formula1>下拉列表!$B$2:$B$38</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2 M3:M1048576">
+      <formula1>下拉列表!$D$2:$D$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1425,185 +1389,170 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
         <v>30</v>
       </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
         <v>31</v>
       </c>
-      <c r="J1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
         <v>32</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>33</v>
       </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="C3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
+      <c r="D3" t="s">
         <v>35</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
         <v>36</v>
       </c>
-      <c r="E3" t="s">
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
         <v>37</v>
       </c>
-      <c r="I3" t="s">
+      <c r="B4" t="s">
         <v>38</v>
       </c>
-      <c r="J3" t="s">
+      <c r="C4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
+      <c r="D4" t="s">
         <v>40</v>
       </c>
-      <c r="B4" t="s">
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
         <v>41</v>
       </c>
-      <c r="E4" t="s">
+      <c r="B5" t="s">
         <v>42</v>
       </c>
-      <c r="I4" t="s">
+      <c r="D5" t="s">
         <v>43</v>
       </c>
-      <c r="J4" t="s">
+      <c r="E5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
         <v>45</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>46</v>
       </c>
-      <c r="I5" t="s">
+      <c r="E6" t="s">
         <v>47</v>
       </c>
-      <c r="J5" t="s">
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
+      <c r="B7" t="s">
         <v>49</v>
       </c>
-      <c r="B6" t="s">
+      <c r="E7" t="s">
         <v>50</v>
       </c>
-      <c r="J6" t="s">
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
+      <c r="B8" t="s">
         <v>52</v>
       </c>
-      <c r="B7" t="s">
+      <c r="E8" t="s">
         <v>53</v>
-      </c>
-      <c r="J7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" t="s">
-        <v>55</v>
-      </c>
-      <c r="J8" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1611,158 +1560,135 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" t="s">
         <v>71</v>
       </c>
-      <c r="B17" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
-        <v>73</v>
-      </c>
-      <c r="B18" t="s">
-        <v>74</v>
-      </c>
-      <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="2:2">
       <c r="B26" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
       <c r="B28" t="s">
-        <v>84</v>
-      </c>
-      <c r="G28" s="1"/>
-    </row>
-    <row r="29" spans="2:7">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
       <c r="B29" t="s">
-        <v>48</v>
-      </c>
-      <c r="G29" s="1"/>
+        <v>44</v>
+      </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
       <c r="B31" t="s">
-        <v>86</v>
-      </c>
-      <c r="G31" s="1"/>
-    </row>
-    <row r="32" spans="2:7">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>87</v>
-      </c>
-      <c r="G32" s="1"/>
+        <v>84</v>
+      </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>51</v>
-      </c>
-      <c r="G34" s="1"/>
-    </row>
-    <row r="35" spans="2:7">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>89</v>
-      </c>
-      <c r="G35" s="1"/>
-    </row>
-    <row r="36" spans="2:7">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>90</v>
-      </c>
-      <c r="G36" s="1"/>
+        <v>87</v>
+      </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="39" spans="7:7">
-      <c r="G39" s="1"/>
-    </row>
-    <row r="40" spans="7:7">
-      <c r="G40" s="1"/>
-    </row>
-    <row r="41" spans="7:7">
-      <c r="G41" s="1"/>
-    </row>
-    <row r="46" spans="7:7">
-      <c r="G46" s="1"/>
-    </row>
-    <row r="47" spans="7:7">
-      <c r="G47" s="1"/>
+        <v>89</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/media/cmdbExcelTemplate/ImportNetworkTemplate.xlsx
+++ b/backend/media/cmdbExcelTemplate/ImportNetworkTemplate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lijiamin/PycharmProjects/BasePlatform/backend/media/cmdbExcelTemplate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E76A48-EFCA-2441-998B-D8B6FDFE6E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A271A2-AF29-5B47-A36C-28ACFE4A2C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-42180" yWindow="2640" windowWidth="33280" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="140" yWindow="920" windowWidth="29940" windowHeight="18560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cmdblist" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="89">
   <si>
     <t>SN号</t>
   </si>
@@ -352,7 +352,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -372,9 +372,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -656,8 +653,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" customWidth="1"/>
-    <col min="3" max="3" width="11.1640625" customWidth="1"/>
+    <col min="2" max="3" width="16.6640625" customWidth="1"/>
     <col min="4" max="4" width="9.5" customWidth="1"/>
     <col min="5" max="5" width="10.5" customWidth="1"/>
     <col min="6" max="6" width="8.5" customWidth="1"/>
@@ -679,7 +675,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>3</v>
@@ -717,18 +713,13 @@
       <c r="O1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="P1" s="2"/>
     </row>
     <row r="2" spans="1:16" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>87</v>
       </c>
       <c r="B2" s="3"/>
-      <c r="C2" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="D2" s="3" t="s">
         <v>14</v>
       </c>
@@ -768,36 +759,30 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>下拉列表!$B$2:$B$39</xm:f>
           </x14:formula1>
-          <xm:sqref>I2 I3:I1048576</xm:sqref>
+          <xm:sqref>I2:I1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>下拉列表!$E$2:$E$8</xm:f>
           </x14:formula1>
-          <xm:sqref>E2 E3:E1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
-          <x14:formula1>
-            <xm:f>下拉列表!$C$2:$C$4</xm:f>
-          </x14:formula1>
-          <xm:sqref>C2 C3:C1048576</xm:sqref>
+          <xm:sqref>E2:E1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000003000000}">
           <x14:formula1>
             <xm:f>下拉列表!$A$2:$A$19</xm:f>
           </x14:formula1>
-          <xm:sqref>D2 D3:D1048576</xm:sqref>
+          <xm:sqref>D2:D1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000004000000}">
           <x14:formula1>
             <xm:f>下拉列表!$D$2:$D$5</xm:f>
           </x14:formula1>
-          <xm:sqref>M2 M3:M1048576</xm:sqref>
+          <xm:sqref>M2:M1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
